--- a/design/tables/ShopRule.xlsx
+++ b/design/tables/ShopRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopRule" sheetId="1" r:id="Rdf2c7eebf01b4bf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopRule" sheetId="1" r:id="Rbec104b9c8f641fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -624,6 +624,20 @@
         <x:v>安全余额上限</x:v>
       </x:c>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>customerWalkSeconds</x:v>
+      </x:c>
+      <x:c r="C27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>仅顾客视觉沿过道移动，不改变经营结算时钟</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/ShopRule.xlsx
+++ b/design/tables/ShopRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopRule" sheetId="1" r:id="Rbec104b9c8f641fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopRule" sheetId="1" r:id="R664c76284b2f4ef5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -638,6 +638,172 @@
         <x:v>仅顾客视觉沿过道移动，不改变经营结算时钟</x:v>
       </x:c>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>workerWalkSeconds</x:v>
+      </x:c>
+      <x:c r="C28" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>walkBobPixels</x:v>
+      </x:c>
+      <x:c r="C29" t="n">
+        <x:v>1.25</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>walkBobFrequency</x:v>
+      </x:c>
+      <x:c r="C30" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>idleBobFrequency</x:v>
+      </x:c>
+      <x:c r="C31" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>idleScaleAmplitude</x:v>
+      </x:c>
+      <x:c r="C32" t="n">
+        <x:v>0.012</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>pickupSeconds</x:v>
+      </x:c>
+      <x:c r="C33" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>pickupLift</x:v>
+      </x:c>
+      <x:c r="C34" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>saleFlightSeconds</x:v>
+      </x:c>
+      <x:c r="C35" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>saleArcHeight</x:v>
+      </x:c>
+      <x:c r="C36" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str"/>
+      <x:c r="B37" t="str"/>
+      <x:c r="C37" t="str"/>
+      <x:c r="D37" t="str"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str"/>
+      <x:c r="B38" t="str"/>
+      <x:c r="C38" t="str"/>
+      <x:c r="D38" t="str"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="n">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>saleTextHideFraction</x:v>
+      </x:c>
+      <x:c r="C39" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="D39" t="str">
+        <x:v>仅成交表现，不参与经营收入或结算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>saleShrinkRatio</x:v>
+      </x:c>
+      <x:c r="C40" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D40" t="str">
+        <x:v>仅成交表现，不参与经营收入或结算</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/ShopRule.xlsx
+++ b/design/tables/ShopRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopRule" sheetId="1" r:id="R664c76284b2f4ef5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopRule" sheetId="1" r:id="R6b718842f4ad4bd6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -311,10 +311,18 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="1" t="str"/>
-      <x:c r="B4" s="1" t="str"/>
-      <x:c r="C4" s="1" t="str"/>
-      <x:c r="D4" s="1" t="str"/>
+      <x:c r="A4" s="1" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="str">
+        <x:v>key</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="str">
+        <x:v>value</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="str">
+        <x:v>note</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="3" t="str">
@@ -394,10 +402,10 @@
         <x:v>arrivalSeconds</x:v>
       </x:c>
       <x:c r="C10" s="1" t="str">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D10" s="1" t="str">
-        <x:v>初始每位顾客间隔秒</x:v>
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
@@ -408,10 +416,10 @@
         <x:v>checkoutSeconds</x:v>
       </x:c>
       <x:c r="C11" s="1" t="str">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D11" s="1" t="str">
-        <x:v>基础收银耗时秒</x:v>
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
@@ -422,10 +430,10 @@
         <x:v>restockSeconds</x:v>
       </x:c>
       <x:c r="C12" s="1" t="str">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D12" s="1" t="str">
-        <x:v>基础补货耗时秒</x:v>
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
@@ -478,10 +486,10 @@
         <x:v>walkRestockSeconds</x:v>
       </x:c>
       <x:c r="C16" s="1" t="str">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D16" s="1" t="str">
-        <x:v>经营可调参数</x:v>
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
@@ -506,10 +514,10 @@
         <x:v>maxShelves</x:v>
       </x:c>
       <x:c r="C18" s="1" t="str">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D18" s="1" t="str">
-        <x:v>经营可调参数</x:v>
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="24" customHeight="1">
@@ -523,7 +531,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D19" s="1" t="str">
-        <x:v>经营可调参数</x:v>
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="24" customHeight="1">
@@ -534,10 +542,10 @@
         <x:v>customerLimit</x:v>
       </x:c>
       <x:c r="C20" s="1" t="str">
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D20" s="1" t="str">
-        <x:v>经营可调参数</x:v>
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="24" customHeight="1">
@@ -576,21 +584,21 @@
         <x:v>visibleStaff</x:v>
       </x:c>
       <x:c r="C23" s="1" t="str">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D23" s="1" t="str">
-        <x:v>经营可调参数</x:v>
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="24" customHeight="1">
       <x:c r="A24" s="1" t="n">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B24" s="1" t="str">
-        <x:v>staffRotateSeconds</x:v>
+        <x:v>uiRefreshSeconds</x:v>
       </x:c>
       <x:c r="C24" s="1" t="str">
-        <x:v>12</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="D24" s="1" t="str">
         <x:v>经营可调参数</x:v>
@@ -598,55 +606,55 @@
     </x:row>
     <x:row r="25" ht="24" customHeight="1">
       <x:c r="A25" s="1" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B25" s="1" t="str">
-        <x:v>uiRefreshSeconds</x:v>
+        <x:v>coinLimit</x:v>
       </x:c>
       <x:c r="C25" s="1" t="str">
-        <x:v>0.2</x:v>
+        <x:v>1000000000</x:v>
       </x:c>
       <x:c r="D25" s="1" t="str">
-        <x:v>经营可调参数</x:v>
+        <x:v>安全余额上限</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="24" customHeight="1">
       <x:c r="A26" s="1" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B26" s="1" t="str">
-        <x:v>coinLimit</x:v>
+        <x:v>customerWalkSeconds</x:v>
       </x:c>
       <x:c r="C26" s="1" t="str">
-        <x:v>1000000000</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D26" s="1" t="str">
-        <x:v>安全余额上限</x:v>
+        <x:v>仅顾客视觉沿过道移动，不改变经营结算时钟</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="n">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>customerWalkSeconds</x:v>
-      </x:c>
-      <x:c r="C27" t="n">
+        <x:v>workerWalkSeconds</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>仅顾客视觉沿过道移动，不改变经营结算时钟</x:v>
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="n">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>workerWalkSeconds</x:v>
-      </x:c>
-      <x:c r="C28" t="n">
-        <x:v>0.8</x:v>
+        <x:v>walkBobPixels</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>1.25</x:v>
       </x:c>
       <x:c r="D28" t="str">
         <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
@@ -654,13 +662,13 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="n">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>walkBobPixels</x:v>
-      </x:c>
-      <x:c r="C29" t="n">
-        <x:v>1.25</x:v>
+        <x:v>walkBobFrequency</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D29" t="str">
         <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
@@ -668,13 +676,13 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="n">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>walkBobFrequency</x:v>
-      </x:c>
-      <x:c r="C30" t="n">
-        <x:v>11</x:v>
+        <x:v>idleBobFrequency</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="D30" t="str">
         <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
@@ -682,13 +690,13 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="n">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>idleBobFrequency</x:v>
-      </x:c>
-      <x:c r="C31" t="n">
-        <x:v>2.4</x:v>
+        <x:v>idleScaleAmplitude</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>0.012</x:v>
       </x:c>
       <x:c r="D31" t="str">
         <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
@@ -696,13 +704,13 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="n">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>idleScaleAmplitude</x:v>
-      </x:c>
-      <x:c r="C32" t="n">
-        <x:v>0.012</x:v>
+        <x:v>pickupSeconds</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>0.65</x:v>
       </x:c>
       <x:c r="D32" t="str">
         <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
@@ -710,13 +718,13 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="n">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>pickupSeconds</x:v>
-      </x:c>
-      <x:c r="C33" t="n">
-        <x:v>0.65</x:v>
+        <x:v>pickupLift</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D33" t="str">
         <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
@@ -724,13 +732,13 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="n">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>pickupLift</x:v>
-      </x:c>
-      <x:c r="C34" t="n">
-        <x:v>14</x:v>
+        <x:v>saleFlightSeconds</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="D34" t="str">
         <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
@@ -738,13 +746,13 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="n">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>saleFlightSeconds</x:v>
-      </x:c>
-      <x:c r="C35" t="n">
-        <x:v>1.4</x:v>
+        <x:v>saleArcHeight</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D35" t="str">
         <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
@@ -752,57 +760,211 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="n">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>saleArcHeight</x:v>
-      </x:c>
-      <x:c r="C36" t="n">
-        <x:v>28</x:v>
+        <x:v>saleTextHideFraction</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>0.3</x:v>
       </x:c>
       <x:c r="D36" t="str">
-        <x:v>仅经营表现，不参与收入、订单、补货或结算时钟</x:v>
+        <x:v>仅成交表现，不参与经营收入或结算</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" t="str"/>
-      <x:c r="B37" t="str"/>
-      <x:c r="C37" t="str"/>
-      <x:c r="D37" t="str"/>
+      <x:c r="A37" t="n">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>saleShrinkRatio</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D37" t="str">
+        <x:v>仅成交表现，不参与经营收入或结算</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" t="str"/>
-      <x:c r="B38" t="str"/>
-      <x:c r="C38" t="str"/>
-      <x:c r="D38" t="str"/>
+      <x:c r="A38" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>restockCarry</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D38" t="str">
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="n">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>saleTextHideFraction</x:v>
-      </x:c>
-      <x:c r="C39" t="n">
-        <x:v>0.3</x:v>
+        <x:v>restockTrigger</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>0.67</x:v>
       </x:c>
       <x:c r="D39" t="str">
-        <x:v>仅成交表现，不参与经营收入或结算</x:v>
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="n">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>saleShrinkRatio</x:v>
-      </x:c>
-      <x:c r="C40" t="n">
-        <x:v>0.5</x:v>
+        <x:v>stockBonusStep</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="D40" t="str">
-        <x:v>仅成交表现，不参与经营收入或结算</x:v>
-      </x:c>
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="n">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>serviceMaxChance</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="D41" t="str">
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>packSpeed</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="D42" t="str">
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>guideSpeed</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="D43" t="str">
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>tidySpeed</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="D44" t="str">
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>workerTaskSeconds</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>shopRowHeight</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>shopViewportHeight</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="D47" t="str">
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>shopScrollWheel</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>researchMax</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50"/>
+      <x:c r="B50"/>
+      <x:c r="C50"/>
+      <x:c r="D50"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51"/>
+      <x:c r="B51"/>
+      <x:c r="C51"/>
+      <x:c r="D51"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/tables/ShopRule.xlsx
+++ b/design/tables/ShopRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopRule" sheetId="1" r:id="R6b718842f4ad4bd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopRule" sheetId="1" r:id="R87d0567973d64de1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -55,11 +55,14 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -966,6 +969,62 @@
       <x:c r="C51"/>
       <x:c r="D51"/>
     </x:row>
+    <x:row r="52" ht="64" customHeight="1">
+      <x:c r="A52" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>offlineIncomeRatio</x:v>
+      </x:c>
+      <x:c r="C52" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D52" s="4" t="str">
+        <x:v>离线净收益折算比例，在线营业不变</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="64" customHeight="1">
+      <x:c r="A53" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B53" t="str">
+        <x:v>offlineBudgetPurchases</x:v>
+      </x:c>
+      <x:c r="C53" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D53" s="4" t="str">
+        <x:v>满2小时预算取后续最低购买费用，短离线按时长分摊</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="64" customHeight="1">
+      <x:c r="A54" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>offlineCompleteBudget</x:v>
+      </x:c>
+      <x:c r="C54" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D54" s="4" t="str">
+        <x:v>全部经营消费完成后的满2小时收益预算</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="64" customHeight="1">
+      <x:c r="A55" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>onlineGapSeconds</x:v>
+      </x:c>
+      <x:c r="C55" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D55" s="4" t="str">
+        <x:v>前台连续停帧达到此秒数按离线结算</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/design/tables/ShopRule.xlsx
+++ b/design/tables/ShopRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopRule" sheetId="1" r:id="R87d0567973d64de1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopRule" sheetId="1" r:id="R3653098edd844ddf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -909,7 +909,7 @@
         <x:v>shopRowHeight</x:v>
       </x:c>
       <x:c r="C46" t="str">
-        <x:v>195</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="D46" t="str">
         <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
@@ -923,7 +923,7 @@
         <x:v>shopViewportHeight</x:v>
       </x:c>
       <x:c r="C47" t="str">
-        <x:v>500</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="D47" t="str">
         <x:v>经营成长1.10.0：原始配置，独立于战斗</x:v>
@@ -958,72 +958,72 @@
       </x:c>
     </x:row>
     <x:row r="50">
-      <x:c r="A50"/>
-      <x:c r="B50"/>
-      <x:c r="C50"/>
-      <x:c r="D50"/>
+      <x:c r="A50" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>offlineIncomeRatio</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>离线净收益折算比例，在线营业不变</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="A51"/>
-      <x:c r="B51"/>
-      <x:c r="C51"/>
-      <x:c r="D51"/>
+      <x:c r="A51" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>offlineBudgetPurchases</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
+        <x:v>满2小时预算取后续最低购买费用，短离线按时长分摊</x:v>
+      </x:c>
     </x:row>
     <x:row r="52" ht="64" customHeight="1">
       <x:c r="A52" t="n">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B52" t="str">
-        <x:v>offlineIncomeRatio</x:v>
-      </x:c>
-      <x:c r="C52" t="n">
-        <x:v>0.5</x:v>
+        <x:v>offlineCompleteBudget</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D52" s="4" t="str">
-        <x:v>离线净收益折算比例，在线营业不变</x:v>
+        <x:v>全部经营消费完成后的满2小时收益预算</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="64" customHeight="1">
       <x:c r="A53" t="n">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B53" t="str">
-        <x:v>offlineBudgetPurchases</x:v>
-      </x:c>
-      <x:c r="C53" t="n">
-        <x:v>2</x:v>
+        <x:v>onlineGapSeconds</x:v>
+      </x:c>
+      <x:c r="C53" t="str">
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D53" s="4" t="str">
-        <x:v>满2小时预算取后续最低购买费用，短离线按时长分摊</x:v>
+        <x:v>前台连续停帧达到此秒数按离线结算</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="64" customHeight="1">
-      <x:c r="A54" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B54" t="str">
-        <x:v>offlineCompleteBudget</x:v>
-      </x:c>
-      <x:c r="C54" t="n">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="D54" s="4" t="str">
-        <x:v>全部经营消费完成后的满2小时收益预算</x:v>
-      </x:c>
+      <x:c r="A54"/>
+      <x:c r="B54"/>
+      <x:c r="C54"/>
+      <x:c r="D54" s="4"/>
     </x:row>
     <x:row r="55" ht="64" customHeight="1">
-      <x:c r="A55" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="B55" t="str">
-        <x:v>onlineGapSeconds</x:v>
-      </x:c>
-      <x:c r="C55" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D55" s="4" t="str">
-        <x:v>前台连续停帧达到此秒数按离线结算</x:v>
-      </x:c>
+      <x:c r="A55"/>
+      <x:c r="B55"/>
+      <x:c r="C55"/>
+      <x:c r="D55" s="4"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design/tables/ShopRule.xlsx
+++ b/design/tables/ShopRule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopRule" sheetId="1" r:id="R3653098edd844ddf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ShopRule" sheetId="1" r:id="R5f41d494ce934fc7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1025,6 +1025,20 @@
       <x:c r="C55"/>
       <x:c r="D55" s="4"/>
     </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>shelfGoodsSlots</x:v>
+      </x:c>
+      <x:c r="C56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D56" t="str">
+        <x:v>每架最多三种商品，共享货架总容量；额外位初始为空</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
